--- a/initial solution/rule-based-final/small_scale_v2/small_rulebased_output.xlsx
+++ b/initial solution/rule-based-final/small_scale_v2/small_rulebased_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -618,11 +618,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>adenotonsillectomy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -632,23 +632,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -673,11 +673,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>rhinoplasty</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -687,28 +687,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -718,7 +718,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,11 +728,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>microlaryngoscopy</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -742,28 +742,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>770</v>
+        <v>710</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -797,18 +797,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>770</v>
+        <v>710</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -838,11 +838,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rhinoplasty</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>785</v>
+        <v>750</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -852,28 +852,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>785</v>
+        <v>750</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -883,7 +883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -893,11 +893,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>buccal mucosa bioppsy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>895</v>
+        <v>755</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -907,23 +907,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>895</v>
+        <v>755</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -938,52 +938,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U0003</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rhinoplasty</t>
+          <t>septoplasty</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>897.5469053480098</v>
+        <v>795</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4530946519902272</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>898</v>
+        <v>795</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -993,47 +993,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U0004</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>adenotonsillectomy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1403.651160099632</v>
+        <v>795</v>
       </c>
       <c r="E11" t="n">
-        <v>516.3488399003677</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1920</v>
+        <v>795</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1048,47 +1048,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U0005</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>adenotonsillectomy</t>
+          <t>buccal mucosa bioppsy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1450.960441761467</v>
+        <v>870</v>
       </c>
       <c r="E12" t="n">
-        <v>469.0395582385331</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1920</v>
+        <v>870</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1103,47 +1103,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>U0003</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ELECTIVE</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>buccal mucosa bioppsy</t>
+          <t>rhinoplasty</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2135</v>
+        <v>897.5469053480098</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3.453094651990227</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2135</v>
+        <v>901</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1158,52 +1158,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>U0004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ELECTIVE</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>septoplasty</t>
+          <t>thyroidectomy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2135</v>
+        <v>1403.651160099632</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>516.3488399003677</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2135</v>
+        <v>1920</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1213,52 +1213,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>U0005</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ELECTIVE</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>adenotonsillectomy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2240</v>
+        <v>1450.960441761467</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>469.0395582385331</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2240</v>
+        <v>1920</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1268,7 +1268,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1278,42 +1278,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>septoplasty</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2285</v>
+        <v>480</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1570</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2285</v>
+        <v>2050</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1323,47 +1323,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U0006</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>buccal mucosa bioppsy</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2525.14949335942</v>
+        <v>520</v>
       </c>
       <c r="E17" t="n">
-        <v>834.8505066405801</v>
+        <v>1590</v>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2110</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>3360</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U0007</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1392,24 +1392,24 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2797.302410783494</v>
+        <v>2180</v>
       </c>
       <c r="E18" t="n">
-        <v>562.6975892165065</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3360</v>
+        <v>2180</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1433,52 +1433,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U0008</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>buccal mucosa bioppsy</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3368.587825959242</v>
+        <v>2180</v>
       </c>
       <c r="E19" t="n">
-        <v>61.41217404075769</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3430</v>
+        <v>2180</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1488,7 +1488,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1498,28 +1498,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>adenotonsillectomy</t>
+          <t>microlaryngoscopy</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3550</v>
+        <v>2255</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3550</v>
+        <v>2255</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1557,25 +1557,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3550</v>
+        <v>2265</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2265</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>3550</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>S7</t>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1598,7 +1598,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1608,28 +1608,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>microlaryngoscopy</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3625</v>
+        <v>915</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1420</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3625</v>
+        <v>2335</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -1653,7 +1653,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1663,37 +1663,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3635</v>
+        <v>915</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1425</v>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2340</v>
+      </c>
+      <c r="I23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>3635</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1708,52 +1708,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>U0006</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ELECTIVE</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>adenotonsillectomy</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3765</v>
+        <v>2525.14949335942</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>834.8505066405801</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3765</v>
+        <v>3360</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1763,7 +1763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>U0009</t>
+          <t>U0007</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>adenotonsillectomy</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3982.25869282768</v>
+        <v>2797.302410783494</v>
       </c>
       <c r="E25" t="n">
-        <v>817.7413071723204</v>
+        <v>562.6975892165065</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1791,24 +1791,24 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4800</v>
+        <v>3360</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -1818,7 +1818,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>U0010</t>
+          <t>U0008</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1828,42 +1828,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>microlaryngoscopy</t>
+          <t>buccal mucosa bioppsy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4411.5780560406</v>
+        <v>3368.587825959242</v>
       </c>
       <c r="E26" t="n">
-        <v>388.4219439593999</v>
+        <v>61.41217404075769</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4800</v>
+        <v>3430</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -1873,7 +1873,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1883,42 +1883,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>sleep apnea diagnosis test</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4930</v>
+        <v>3530</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4930</v>
+        <v>3530</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -1928,7 +1928,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1938,42 +1938,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>adenotonsillectomy</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1920</v>
+        <v>525</v>
       </c>
       <c r="E28" t="n">
-        <v>3090</v>
+        <v>3046</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5010</v>
+        <v>3571</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -1983,7 +1983,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1993,37 +1993,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sleep apnea diagnosis test</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2005</v>
+        <v>1920</v>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>1726</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5105</v>
+        <v>3646</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2048,42 +2048,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5120</v>
+        <v>3360</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5120</v>
+        <v>3720</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2093,7 +2093,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>U0011</t>
+          <t>U0009</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2103,17 +2103,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>adenotonsillectomy</t>
+          <t>thyroidectomy</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5523.720070880443</v>
+        <v>3982.25869282768</v>
       </c>
       <c r="E31" t="n">
-        <v>716.279929119557</v>
+        <v>817.7413071723204</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6240</v>
+        <v>4800</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>S3</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>S1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2148,7 +2148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>U0012</t>
+          <t>U0010</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>microlaryngoscopy</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5534.556080513911</v>
+        <v>4411.5780560406</v>
       </c>
       <c r="E32" t="n">
-        <v>705.4439194860888</v>
+        <v>388.4219439593999</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2176,19 +2176,19 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6240</v>
+        <v>4800</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>U0013</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5538.994912093265</v>
+        <v>4990</v>
       </c>
       <c r="E33" t="n">
-        <v>771.0050879067348</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6310</v>
+        <v>4990</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -2258,42 +2258,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>U0014</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>rhinoplasty</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6095.74903293209</v>
+        <v>4990</v>
       </c>
       <c r="E34" t="n">
-        <v>224.2509670679101</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6320</v>
+        <v>4990</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2313,7 +2313,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2323,42 +2323,42 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>septoplasty</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3360</v>
+        <v>5120</v>
       </c>
       <c r="E35" t="n">
-        <v>3130</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6490</v>
+        <v>5120</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2368,7 +2368,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2378,37 +2378,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>septoplasty</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6490</v>
+        <v>5120</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6490</v>
+        <v>5120</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>S3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>S8</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2423,12 +2423,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>U0011</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ELECTIVE</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2437,24 +2437,24 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6595</v>
+        <v>5523.720070880443</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>716.279929119557</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6596</v>
+        <v>6240</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2478,47 +2478,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>U0012</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ELECTIVE</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sleep apnea diagnosis test</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3360</v>
+        <v>5534.556080513911</v>
       </c>
       <c r="E38" t="n">
-        <v>3311</v>
+        <v>705.4439194860888</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6671</v>
+        <v>6240</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2533,7 +2533,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>U0015</t>
+          <t>U0013</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2543,42 +2543,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6716.91192876217</v>
+        <v>5538.994912093265</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08807123783026327</v>
+        <v>771.0050879067348</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6717</v>
+        <v>6310</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2588,7 +2588,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>U0016</t>
+          <t>U0014</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2598,32 +2598,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rhinoplasty</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6837.215537148585</v>
+        <v>6095.74903293209</v>
       </c>
       <c r="E40" t="n">
-        <v>3722.784462851415</v>
+        <v>229.2509670679101</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10560</v>
+        <v>6325</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2643,52 +2643,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>U0017</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>URGENT</t>
+          <t>ELECTIVE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>rhinoplasty</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8181.034666227051</v>
+        <v>6605</v>
       </c>
       <c r="E41" t="n">
-        <v>2378.965333772949</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10560</v>
+        <v>6605</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2698,7 +2698,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>U0018</t>
+          <t>U0015</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2708,42 +2708,42 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8308.416388618318</v>
+        <v>6716.91192876217</v>
       </c>
       <c r="E42" t="n">
-        <v>2326.583611381682</v>
+        <v>0.08807123783026327</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10635</v>
+        <v>6717</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -2753,7 +2753,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>U0019</t>
+          <t>U0016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8850.640780039195</v>
+        <v>6837.215537148585</v>
       </c>
       <c r="E43" t="n">
-        <v>1815.359219960805</v>
+        <v>3722.784462851415</v>
       </c>
       <c r="F43" t="n">
         <v>7</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10666</v>
+        <v>10560</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -2802,6 +2802,171 @@
         </is>
       </c>
       <c r="M43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>U0017</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>endoscopic sinus</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8181.034666227051</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2378.965333772949</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>10560</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>U0018</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>thyroidectomy</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8308.416388618318</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2326.583611381682</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>10635</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>U0019</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>rhinoplasty</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8850.640780039195</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1819.359219960805</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>10670</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
         <v>3</v>
       </c>
     </row>
